--- a/irrbb_calc/output/irrbb_report.xlsx
+++ b/irrbb_calc/output/irrbb_report.xlsx
@@ -494,10 +494,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>528545794.34</v>
+        <v>537319929.91</v>
       </c>
       <c r="E2" t="n">
-        <v>528545794.34</v>
+        <v>537319929.91</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>2094998346.9</v>
+        <v>2171503039.11</v>
       </c>
       <c r="I2" t="n">
-        <v>2094998346.9</v>
+        <v>2171503039.11</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -533,28 +533,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>528545794.34</v>
+        <v>537319929.91</v>
       </c>
       <c r="E3" t="n">
-        <v>504658759.42</v>
+        <v>512211372.01</v>
       </c>
       <c r="F3" t="n">
-        <v>-23887034.91999996</v>
+        <v>-25108557.89999998</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.99058624333333</v>
+        <v>-2.092379824999998</v>
       </c>
       <c r="H3" t="n">
-        <v>2094998346.9</v>
+        <v>2171503039.11</v>
       </c>
       <c r="I3" t="n">
-        <v>2129901580.06</v>
+        <v>2206059950.06</v>
       </c>
       <c r="J3" t="n">
-        <v>34903233.15999985</v>
+        <v>34556910.94999981</v>
       </c>
       <c r="K3" t="n">
-        <v>2.908602763333321</v>
+        <v>2.879742579166651</v>
       </c>
     </row>
     <row r="4">
@@ -572,28 +572,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>528545794.34</v>
+        <v>537319929.91</v>
       </c>
       <c r="E4" t="n">
-        <v>510628634.11</v>
+        <v>521475205.63</v>
       </c>
       <c r="F4" t="n">
-        <v>-17917160.22999996</v>
+        <v>-15844724.27999997</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.49309668583333</v>
+        <v>-1.320393689999998</v>
       </c>
       <c r="H4" t="n">
-        <v>2094998346.9</v>
+        <v>2171503039.11</v>
       </c>
       <c r="I4" t="n">
-        <v>2147240980.85</v>
+        <v>2226642923.68</v>
       </c>
       <c r="J4" t="n">
-        <v>52242633.94999981</v>
+        <v>55139884.56999969</v>
       </c>
       <c r="K4" t="n">
-        <v>4.353552829166651</v>
+        <v>4.594990380833308</v>
       </c>
     </row>
     <row r="5">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>528545794.34</v>
+        <v>537319929.91</v>
       </c>
       <c r="E5" t="n">
-        <v>486337695.77</v>
+        <v>500370371.04</v>
       </c>
       <c r="F5" t="n">
-        <v>-42208098.56999999</v>
+        <v>-36949558.86999995</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.5173415475</v>
+        <v>-3.079129905833329</v>
       </c>
       <c r="H5" t="n">
-        <v>2094998346.9</v>
+        <v>2171503039.11</v>
       </c>
       <c r="I5" t="n">
-        <v>2229316540.08</v>
+        <v>2312912010.57</v>
       </c>
       <c r="J5" t="n">
-        <v>134318193.1799998</v>
+        <v>141408971.46</v>
       </c>
       <c r="K5" t="n">
-        <v>11.19318276499999</v>
+        <v>11.784080955</v>
       </c>
     </row>
     <row r="6">
@@ -650,28 +650,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>528545794.34</v>
+        <v>537319929.91</v>
       </c>
       <c r="E6" t="n">
-        <v>567239502.7</v>
+        <v>570524821.17</v>
       </c>
       <c r="F6" t="n">
-        <v>38693708.36000007</v>
+        <v>33204891.25999999</v>
       </c>
       <c r="G6" t="n">
-        <v>3.224475696666672</v>
+        <v>2.767074271666666</v>
       </c>
       <c r="H6" t="n">
-        <v>2094998346.9</v>
+        <v>2171503039.11</v>
       </c>
       <c r="I6" t="n">
-        <v>1973036350.02</v>
+        <v>2041758857.86</v>
       </c>
       <c r="J6" t="n">
-        <v>-121961996.8800001</v>
+        <v>-129744181.2500002</v>
       </c>
       <c r="K6" t="n">
-        <v>-10.16349974000001</v>
+        <v>-10.81201510416669</v>
       </c>
     </row>
     <row r="7">
@@ -689,28 +689,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>528545794.34</v>
+        <v>537319929.91</v>
       </c>
       <c r="E7" t="n">
-        <v>530093342.62</v>
+        <v>542004735.38</v>
       </c>
       <c r="F7" t="n">
-        <v>1547548.280000031</v>
+        <v>4684805.470000029</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1289623566666692</v>
+        <v>0.3904004558333357</v>
       </c>
       <c r="H7" t="n">
-        <v>2094998346.9</v>
+        <v>2171503039.11</v>
       </c>
       <c r="I7" t="n">
-        <v>2116476598.37</v>
+        <v>2196126359.83</v>
       </c>
       <c r="J7" t="n">
-        <v>21478251.46999979</v>
+        <v>24623320.71999979</v>
       </c>
       <c r="K7" t="n">
-        <v>1.789854289166649</v>
+        <v>2.051943393333316</v>
       </c>
     </row>
     <row r="8">
@@ -728,28 +728,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>528545794.34</v>
+        <v>537319929.91</v>
       </c>
       <c r="E8" t="n">
-        <v>523259508.19</v>
+        <v>528761317.8</v>
       </c>
       <c r="F8" t="n">
-        <v>-5286286.149999976</v>
+        <v>-8558612.109999955</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4405238458333314</v>
+        <v>-0.7132176758333296</v>
       </c>
       <c r="H8" t="n">
-        <v>2094998346.9</v>
+        <v>2171503039.11</v>
       </c>
       <c r="I8" t="n">
-        <v>2073987061.46</v>
+        <v>2147302576.07</v>
       </c>
       <c r="J8" t="n">
-        <v>-21011285.44000006</v>
+        <v>-24200463.0400002</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.750940453333338</v>
+        <v>-2.01670525333335</v>
       </c>
     </row>
     <row r="9">
@@ -767,28 +767,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>528545794.34</v>
+        <v>537319929.91</v>
       </c>
       <c r="E9" t="n">
-        <v>552265384.9</v>
+        <v>561357106.7</v>
       </c>
       <c r="F9" t="n">
-        <v>23719590.56</v>
+        <v>24037176.79000008</v>
       </c>
       <c r="G9" t="n">
-        <v>1.976632546666667</v>
+        <v>2.00309806583334</v>
       </c>
       <c r="H9" t="n">
-        <v>2094998346.9</v>
+        <v>2171503039.11</v>
       </c>
       <c r="I9" t="n">
-        <v>2049526125.86</v>
+        <v>2125095296.74</v>
       </c>
       <c r="J9" t="n">
-        <v>-45472221.0400002</v>
+        <v>-46407742.37000012</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.78935175333335</v>
+        <v>-3.867311864166677</v>
       </c>
     </row>
   </sheetData>
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>528545794.34</v>
+        <v>537319929.91</v>
       </c>
       <c r="D2" t="n">
-        <v>528545794.34</v>
+        <v>537319929.91</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -873,16 +873,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>528545794.34</v>
+        <v>537319929.91</v>
       </c>
       <c r="D3" t="n">
-        <v>504658759.42</v>
+        <v>512211372.01</v>
       </c>
       <c r="E3" t="n">
-        <v>-23887034.91999996</v>
+        <v>-25108557.89999998</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.99058624333333</v>
+        <v>-2.092379824999998</v>
       </c>
     </row>
     <row r="4">
@@ -897,16 +897,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>528545794.34</v>
+        <v>537319929.91</v>
       </c>
       <c r="D4" t="n">
-        <v>510628634.11</v>
+        <v>521475205.63</v>
       </c>
       <c r="E4" t="n">
-        <v>-17917160.22999996</v>
+        <v>-15844724.27999997</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.49309668583333</v>
+        <v>-1.320393689999998</v>
       </c>
     </row>
     <row r="5">
@@ -921,16 +921,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>528545794.34</v>
+        <v>537319929.91</v>
       </c>
       <c r="D5" t="n">
-        <v>486337695.77</v>
+        <v>500370371.04</v>
       </c>
       <c r="E5" t="n">
-        <v>-42208098.56999999</v>
+        <v>-36949558.86999995</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.5173415475</v>
+        <v>-3.079129905833329</v>
       </c>
     </row>
     <row r="6">
@@ -945,16 +945,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>528545794.34</v>
+        <v>537319929.91</v>
       </c>
       <c r="D6" t="n">
-        <v>567239502.7</v>
+        <v>570524821.17</v>
       </c>
       <c r="E6" t="n">
-        <v>38693708.36000007</v>
+        <v>33204891.25999999</v>
       </c>
       <c r="F6" t="n">
-        <v>3.224475696666672</v>
+        <v>2.767074271666666</v>
       </c>
     </row>
     <row r="7">
@@ -969,16 +969,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>528545794.34</v>
+        <v>537319929.91</v>
       </c>
       <c r="D7" t="n">
-        <v>530093342.62</v>
+        <v>542004735.38</v>
       </c>
       <c r="E7" t="n">
-        <v>1547548.280000031</v>
+        <v>4684805.470000029</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1289623566666692</v>
+        <v>0.3904004558333357</v>
       </c>
     </row>
     <row r="8">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>528545794.34</v>
+        <v>537319929.91</v>
       </c>
       <c r="D8" t="n">
-        <v>523259508.19</v>
+        <v>528761317.8</v>
       </c>
       <c r="E8" t="n">
-        <v>-5286286.149999976</v>
+        <v>-8558612.109999955</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4405238458333314</v>
+        <v>-0.7132176758333296</v>
       </c>
     </row>
     <row r="9">
@@ -1017,16 +1017,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>528545794.34</v>
+        <v>537319929.91</v>
       </c>
       <c r="D9" t="n">
-        <v>552265384.9</v>
+        <v>561357106.7</v>
       </c>
       <c r="E9" t="n">
-        <v>23719590.56</v>
+        <v>24037176.79000008</v>
       </c>
       <c r="F9" t="n">
-        <v>1.976632546666667</v>
+        <v>2.00309806583334</v>
       </c>
     </row>
   </sheetData>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2094998346.9</v>
+        <v>2171503039.11</v>
       </c>
       <c r="D2" t="n">
-        <v>2094998346.9</v>
+        <v>2171503039.11</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2094998346.9</v>
+        <v>2171503039.11</v>
       </c>
       <c r="D3" t="n">
-        <v>2129901580.06</v>
+        <v>2206059950.06</v>
       </c>
       <c r="E3" t="n">
-        <v>34903233.15999985</v>
+        <v>34556910.94999981</v>
       </c>
       <c r="F3" t="n">
-        <v>2.908602763333321</v>
+        <v>2.879742579166651</v>
       </c>
     </row>
     <row r="4">
@@ -1135,16 +1135,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2094998346.9</v>
+        <v>2171503039.11</v>
       </c>
       <c r="D4" t="n">
-        <v>2147240980.85</v>
+        <v>2226642923.68</v>
       </c>
       <c r="E4" t="n">
-        <v>52242633.94999981</v>
+        <v>55139884.56999969</v>
       </c>
       <c r="F4" t="n">
-        <v>4.353552829166651</v>
+        <v>4.594990380833308</v>
       </c>
     </row>
     <row r="5">
@@ -1159,16 +1159,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2094998346.9</v>
+        <v>2171503039.11</v>
       </c>
       <c r="D5" t="n">
-        <v>2229316540.08</v>
+        <v>2312912010.57</v>
       </c>
       <c r="E5" t="n">
-        <v>134318193.1799998</v>
+        <v>141408971.46</v>
       </c>
       <c r="F5" t="n">
-        <v>11.19318276499999</v>
+        <v>11.784080955</v>
       </c>
     </row>
     <row r="6">
@@ -1183,16 +1183,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2094998346.9</v>
+        <v>2171503039.11</v>
       </c>
       <c r="D6" t="n">
-        <v>1973036350.02</v>
+        <v>2041758857.86</v>
       </c>
       <c r="E6" t="n">
-        <v>-121961996.8800001</v>
+        <v>-129744181.2500002</v>
       </c>
       <c r="F6" t="n">
-        <v>-10.16349974000001</v>
+        <v>-10.81201510416669</v>
       </c>
     </row>
     <row r="7">
@@ -1207,16 +1207,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2094998346.9</v>
+        <v>2171503039.11</v>
       </c>
       <c r="D7" t="n">
-        <v>2116476598.37</v>
+        <v>2196126359.83</v>
       </c>
       <c r="E7" t="n">
-        <v>21478251.46999979</v>
+        <v>24623320.71999979</v>
       </c>
       <c r="F7" t="n">
-        <v>1.789854289166649</v>
+        <v>2.051943393333316</v>
       </c>
     </row>
     <row r="8">
@@ -1231,16 +1231,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2094998346.9</v>
+        <v>2171503039.11</v>
       </c>
       <c r="D8" t="n">
-        <v>2073987061.46</v>
+        <v>2147302576.07</v>
       </c>
       <c r="E8" t="n">
-        <v>-21011285.44000006</v>
+        <v>-24200463.0400002</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.750940453333338</v>
+        <v>-2.01670525333335</v>
       </c>
     </row>
     <row r="9">
@@ -1255,16 +1255,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2094998346.9</v>
+        <v>2171503039.11</v>
       </c>
       <c r="D9" t="n">
-        <v>2049526125.86</v>
+        <v>2125095296.74</v>
       </c>
       <c r="E9" t="n">
-        <v>-45472221.0400002</v>
+        <v>-46407742.37000012</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.78935175333335</v>
+        <v>-3.867311864166677</v>
       </c>
     </row>
   </sheetData>

--- a/irrbb_calc/output/irrbb_report.xlsx
+++ b/irrbb_calc/output/irrbb_report.xlsx
@@ -494,10 +494,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>537319929.91</v>
+        <v>464115514.96</v>
       </c>
       <c r="E2" t="n">
-        <v>537319929.91</v>
+        <v>464115514.96</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>2171503039.11</v>
+        <v>1916356061.54</v>
       </c>
       <c r="I2" t="n">
-        <v>2171503039.11</v>
+        <v>1916356061.54</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -533,28 +533,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>537319929.91</v>
+        <v>464115514.96</v>
       </c>
       <c r="E3" t="n">
-        <v>512211372.01</v>
+        <v>438331502.68</v>
       </c>
       <c r="F3" t="n">
-        <v>-25108557.89999998</v>
+        <v>-25784012.27999997</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.092379824999998</v>
+        <v>-2.148667689999998</v>
       </c>
       <c r="H3" t="n">
-        <v>2171503039.11</v>
+        <v>1916356061.54</v>
       </c>
       <c r="I3" t="n">
-        <v>2206059950.06</v>
+        <v>1951602159.12</v>
       </c>
       <c r="J3" t="n">
-        <v>34556910.94999981</v>
+        <v>35246097.57999992</v>
       </c>
       <c r="K3" t="n">
-        <v>2.879742579166651</v>
+        <v>2.937174798333327</v>
       </c>
     </row>
     <row r="4">
@@ -572,28 +572,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>537319929.91</v>
+        <v>464115514.96</v>
       </c>
       <c r="E4" t="n">
-        <v>521475205.63</v>
+        <v>447267377.49</v>
       </c>
       <c r="F4" t="n">
-        <v>-15844724.27999997</v>
+        <v>-16848137.46999997</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.320393689999998</v>
+        <v>-1.404011455833331</v>
       </c>
       <c r="H4" t="n">
-        <v>2171503039.11</v>
+        <v>1916356061.54</v>
       </c>
       <c r="I4" t="n">
-        <v>2226642923.68</v>
+        <v>1968379211.04</v>
       </c>
       <c r="J4" t="n">
-        <v>55139884.56999969</v>
+        <v>52023149.5</v>
       </c>
       <c r="K4" t="n">
-        <v>4.594990380833308</v>
+        <v>4.335262458333333</v>
       </c>
     </row>
     <row r="5">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>537319929.91</v>
+        <v>464115514.96</v>
       </c>
       <c r="E5" t="n">
-        <v>500370371.04</v>
+        <v>424713058.09</v>
       </c>
       <c r="F5" t="n">
-        <v>-36949558.86999995</v>
+        <v>-39402456.87</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.079129905833329</v>
+        <v>-3.2835380725</v>
       </c>
       <c r="H5" t="n">
-        <v>2171503039.11</v>
+        <v>1916356061.54</v>
       </c>
       <c r="I5" t="n">
-        <v>2312912010.57</v>
+        <v>2049892910.4</v>
       </c>
       <c r="J5" t="n">
-        <v>141408971.46</v>
+        <v>133536848.8600001</v>
       </c>
       <c r="K5" t="n">
-        <v>11.784080955</v>
+        <v>11.12807073833334</v>
       </c>
     </row>
     <row r="6">
@@ -650,28 +650,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>537319929.91</v>
+        <v>464115514.96</v>
       </c>
       <c r="E6" t="n">
-        <v>570524821.17</v>
+        <v>499832517.6</v>
       </c>
       <c r="F6" t="n">
-        <v>33204891.25999999</v>
+        <v>35717002.64000005</v>
       </c>
       <c r="G6" t="n">
-        <v>2.767074271666666</v>
+        <v>2.97641688666667</v>
       </c>
       <c r="H6" t="n">
-        <v>2171503039.11</v>
+        <v>1916356061.54</v>
       </c>
       <c r="I6" t="n">
-        <v>2041758857.86</v>
+        <v>1794233839.47</v>
       </c>
       <c r="J6" t="n">
-        <v>-129744181.2500002</v>
+        <v>-122122222.0699999</v>
       </c>
       <c r="K6" t="n">
-        <v>-10.81201510416669</v>
+        <v>-10.17685183916666</v>
       </c>
     </row>
     <row r="7">
@@ -689,28 +689,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>537319929.91</v>
+        <v>464115514.96</v>
       </c>
       <c r="E7" t="n">
-        <v>542004735.38</v>
+        <v>468775395.59</v>
       </c>
       <c r="F7" t="n">
-        <v>4684805.470000029</v>
+        <v>4659880.629999995</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3904004558333357</v>
+        <v>0.3883233858333329</v>
       </c>
       <c r="H7" t="n">
-        <v>2171503039.11</v>
+        <v>1916356061.54</v>
       </c>
       <c r="I7" t="n">
-        <v>2196126359.83</v>
+        <v>1937223352.26</v>
       </c>
       <c r="J7" t="n">
-        <v>24623320.71999979</v>
+        <v>20867290.72000003</v>
       </c>
       <c r="K7" t="n">
-        <v>2.051943393333316</v>
+        <v>1.738940893333336</v>
       </c>
     </row>
     <row r="8">
@@ -728,28 +728,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>537319929.91</v>
+        <v>464115514.96</v>
       </c>
       <c r="E8" t="n">
-        <v>528761317.8</v>
+        <v>455959739.47</v>
       </c>
       <c r="F8" t="n">
-        <v>-8558612.109999955</v>
+        <v>-8155775.48999995</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7132176758333296</v>
+        <v>-0.6796479574999958</v>
       </c>
       <c r="H8" t="n">
-        <v>2171503039.11</v>
+        <v>1916356061.54</v>
       </c>
       <c r="I8" t="n">
-        <v>2147302576.07</v>
+        <v>1895858582.06</v>
       </c>
       <c r="J8" t="n">
-        <v>-24200463.0400002</v>
+        <v>-20497479.48000002</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.01670525333335</v>
+        <v>-1.708123290000002</v>
       </c>
     </row>
     <row r="9">
@@ -767,28 +767,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>537319929.91</v>
+        <v>464115514.96</v>
       </c>
       <c r="E9" t="n">
-        <v>561357106.7</v>
+        <v>489070373.65</v>
       </c>
       <c r="F9" t="n">
-        <v>24037176.79000008</v>
+        <v>24954858.69</v>
       </c>
       <c r="G9" t="n">
-        <v>2.00309806583334</v>
+        <v>2.0795715575</v>
       </c>
       <c r="H9" t="n">
-        <v>2171503039.11</v>
+        <v>1916356061.54</v>
       </c>
       <c r="I9" t="n">
-        <v>2125095296.74</v>
+        <v>1870259103.15</v>
       </c>
       <c r="J9" t="n">
-        <v>-46407742.37000012</v>
+        <v>-46096958.38999987</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.867311864166677</v>
+        <v>-3.841413199166656</v>
       </c>
     </row>
   </sheetData>
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>537319929.91</v>
+        <v>464115514.96</v>
       </c>
       <c r="D2" t="n">
-        <v>537319929.91</v>
+        <v>464115514.96</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -873,16 +873,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>537319929.91</v>
+        <v>464115514.96</v>
       </c>
       <c r="D3" t="n">
-        <v>512211372.01</v>
+        <v>438331502.68</v>
       </c>
       <c r="E3" t="n">
-        <v>-25108557.89999998</v>
+        <v>-25784012.27999997</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.092379824999998</v>
+        <v>-2.148667689999998</v>
       </c>
     </row>
     <row r="4">
@@ -897,16 +897,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>537319929.91</v>
+        <v>464115514.96</v>
       </c>
       <c r="D4" t="n">
-        <v>521475205.63</v>
+        <v>447267377.49</v>
       </c>
       <c r="E4" t="n">
-        <v>-15844724.27999997</v>
+        <v>-16848137.46999997</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.320393689999998</v>
+        <v>-1.404011455833331</v>
       </c>
     </row>
     <row r="5">
@@ -921,16 +921,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>537319929.91</v>
+        <v>464115514.96</v>
       </c>
       <c r="D5" t="n">
-        <v>500370371.04</v>
+        <v>424713058.09</v>
       </c>
       <c r="E5" t="n">
-        <v>-36949558.86999995</v>
+        <v>-39402456.87</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.079129905833329</v>
+        <v>-3.2835380725</v>
       </c>
     </row>
     <row r="6">
@@ -945,16 +945,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>537319929.91</v>
+        <v>464115514.96</v>
       </c>
       <c r="D6" t="n">
-        <v>570524821.17</v>
+        <v>499832517.6</v>
       </c>
       <c r="E6" t="n">
-        <v>33204891.25999999</v>
+        <v>35717002.64000005</v>
       </c>
       <c r="F6" t="n">
-        <v>2.767074271666666</v>
+        <v>2.97641688666667</v>
       </c>
     </row>
     <row r="7">
@@ -969,16 +969,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>537319929.91</v>
+        <v>464115514.96</v>
       </c>
       <c r="D7" t="n">
-        <v>542004735.38</v>
+        <v>468775395.59</v>
       </c>
       <c r="E7" t="n">
-        <v>4684805.470000029</v>
+        <v>4659880.629999995</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3904004558333357</v>
+        <v>0.3883233858333329</v>
       </c>
     </row>
     <row r="8">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>537319929.91</v>
+        <v>464115514.96</v>
       </c>
       <c r="D8" t="n">
-        <v>528761317.8</v>
+        <v>455959739.47</v>
       </c>
       <c r="E8" t="n">
-        <v>-8558612.109999955</v>
+        <v>-8155775.48999995</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7132176758333296</v>
+        <v>-0.6796479574999958</v>
       </c>
     </row>
     <row r="9">
@@ -1017,16 +1017,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>537319929.91</v>
+        <v>464115514.96</v>
       </c>
       <c r="D9" t="n">
-        <v>561357106.7</v>
+        <v>489070373.65</v>
       </c>
       <c r="E9" t="n">
-        <v>24037176.79000008</v>
+        <v>24954858.69</v>
       </c>
       <c r="F9" t="n">
-        <v>2.00309806583334</v>
+        <v>2.0795715575</v>
       </c>
     </row>
   </sheetData>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2171503039.11</v>
+        <v>1916356061.54</v>
       </c>
       <c r="D2" t="n">
-        <v>2171503039.11</v>
+        <v>1916356061.54</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2171503039.11</v>
+        <v>1916356061.54</v>
       </c>
       <c r="D3" t="n">
-        <v>2206059950.06</v>
+        <v>1951602159.12</v>
       </c>
       <c r="E3" t="n">
-        <v>34556910.94999981</v>
+        <v>35246097.57999992</v>
       </c>
       <c r="F3" t="n">
-        <v>2.879742579166651</v>
+        <v>2.937174798333327</v>
       </c>
     </row>
     <row r="4">
@@ -1135,16 +1135,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2171503039.11</v>
+        <v>1916356061.54</v>
       </c>
       <c r="D4" t="n">
-        <v>2226642923.68</v>
+        <v>1968379211.04</v>
       </c>
       <c r="E4" t="n">
-        <v>55139884.56999969</v>
+        <v>52023149.5</v>
       </c>
       <c r="F4" t="n">
-        <v>4.594990380833308</v>
+        <v>4.335262458333333</v>
       </c>
     </row>
     <row r="5">
@@ -1159,16 +1159,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2171503039.11</v>
+        <v>1916356061.54</v>
       </c>
       <c r="D5" t="n">
-        <v>2312912010.57</v>
+        <v>2049892910.4</v>
       </c>
       <c r="E5" t="n">
-        <v>141408971.46</v>
+        <v>133536848.8600001</v>
       </c>
       <c r="F5" t="n">
-        <v>11.784080955</v>
+        <v>11.12807073833334</v>
       </c>
     </row>
     <row r="6">
@@ -1183,16 +1183,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2171503039.11</v>
+        <v>1916356061.54</v>
       </c>
       <c r="D6" t="n">
-        <v>2041758857.86</v>
+        <v>1794233839.47</v>
       </c>
       <c r="E6" t="n">
-        <v>-129744181.2500002</v>
+        <v>-122122222.0699999</v>
       </c>
       <c r="F6" t="n">
-        <v>-10.81201510416669</v>
+        <v>-10.17685183916666</v>
       </c>
     </row>
     <row r="7">
@@ -1207,16 +1207,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2171503039.11</v>
+        <v>1916356061.54</v>
       </c>
       <c r="D7" t="n">
-        <v>2196126359.83</v>
+        <v>1937223352.26</v>
       </c>
       <c r="E7" t="n">
-        <v>24623320.71999979</v>
+        <v>20867290.72000003</v>
       </c>
       <c r="F7" t="n">
-        <v>2.051943393333316</v>
+        <v>1.738940893333336</v>
       </c>
     </row>
     <row r="8">
@@ -1231,16 +1231,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2171503039.11</v>
+        <v>1916356061.54</v>
       </c>
       <c r="D8" t="n">
-        <v>2147302576.07</v>
+        <v>1895858582.06</v>
       </c>
       <c r="E8" t="n">
-        <v>-24200463.0400002</v>
+        <v>-20497479.48000002</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.01670525333335</v>
+        <v>-1.708123290000002</v>
       </c>
     </row>
     <row r="9">
@@ -1255,16 +1255,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2171503039.11</v>
+        <v>1916356061.54</v>
       </c>
       <c r="D9" t="n">
-        <v>2125095296.74</v>
+        <v>1870259103.15</v>
       </c>
       <c r="E9" t="n">
-        <v>-46407742.37000012</v>
+        <v>-46096958.38999987</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.867311864166677</v>
+        <v>-3.841413199166656</v>
       </c>
     </row>
   </sheetData>

--- a/irrbb_calc/output/irrbb_report.xlsx
+++ b/irrbb_calc/output/irrbb_report.xlsx
@@ -494,10 +494,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>464115514.96</v>
+        <v>469321503.96</v>
       </c>
       <c r="E2" t="n">
-        <v>464115514.96</v>
+        <v>469321503.96</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>1916356061.54</v>
+        <v>1974746196.97</v>
       </c>
       <c r="I2" t="n">
-        <v>1916356061.54</v>
+        <v>1974746196.97</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -533,28 +533,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>464115514.96</v>
+        <v>469321503.96</v>
       </c>
       <c r="E3" t="n">
-        <v>438331502.68</v>
+        <v>443546752.7</v>
       </c>
       <c r="F3" t="n">
-        <v>-25784012.27999997</v>
+        <v>-25774751.25999999</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.148667689999998</v>
+        <v>-2.147895938333332</v>
       </c>
       <c r="H3" t="n">
-        <v>1916356061.54</v>
+        <v>1974746196.97</v>
       </c>
       <c r="I3" t="n">
-        <v>1951602159.12</v>
+        <v>2007074920.46</v>
       </c>
       <c r="J3" t="n">
-        <v>35246097.57999992</v>
+        <v>32328723.49000001</v>
       </c>
       <c r="K3" t="n">
-        <v>2.937174798333327</v>
+        <v>2.694060290833334</v>
       </c>
     </row>
     <row r="4">
@@ -572,28 +572,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>464115514.96</v>
+        <v>469321503.96</v>
       </c>
       <c r="E4" t="n">
-        <v>447267377.49</v>
+        <v>453243451.72</v>
       </c>
       <c r="F4" t="n">
-        <v>-16848137.46999997</v>
+        <v>-16078052.23999995</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.404011455833331</v>
+        <v>-1.339837686666663</v>
       </c>
       <c r="H4" t="n">
-        <v>1916356061.54</v>
+        <v>1974746196.97</v>
       </c>
       <c r="I4" t="n">
-        <v>1968379211.04</v>
+        <v>2024574398.13</v>
       </c>
       <c r="J4" t="n">
-        <v>52023149.5</v>
+        <v>49828201.16000009</v>
       </c>
       <c r="K4" t="n">
-        <v>4.335262458333333</v>
+        <v>4.152350096666674</v>
       </c>
     </row>
     <row r="5">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>464115514.96</v>
+        <v>469321503.96</v>
       </c>
       <c r="E5" t="n">
-        <v>424713058.09</v>
+        <v>431761757.49</v>
       </c>
       <c r="F5" t="n">
-        <v>-39402456.87</v>
+        <v>-37559746.46999997</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.2835380725</v>
+        <v>-3.129978872499997</v>
       </c>
       <c r="H5" t="n">
-        <v>1916356061.54</v>
+        <v>1974746196.97</v>
       </c>
       <c r="I5" t="n">
-        <v>2049892910.4</v>
+        <v>2102562803.04</v>
       </c>
       <c r="J5" t="n">
-        <v>133536848.8600001</v>
+        <v>127816606.0699999</v>
       </c>
       <c r="K5" t="n">
-        <v>11.12807073833334</v>
+        <v>10.65138383916666</v>
       </c>
     </row>
     <row r="6">
@@ -650,28 +650,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>464115514.96</v>
+        <v>469321503.96</v>
       </c>
       <c r="E6" t="n">
-        <v>499832517.6</v>
+        <v>503296385.94</v>
       </c>
       <c r="F6" t="n">
-        <v>35717002.64000005</v>
+        <v>33974881.98000002</v>
       </c>
       <c r="G6" t="n">
-        <v>2.97641688666667</v>
+        <v>2.831240165000002</v>
       </c>
       <c r="H6" t="n">
-        <v>1916356061.54</v>
+        <v>1974746196.97</v>
       </c>
       <c r="I6" t="n">
-        <v>1794233839.47</v>
+        <v>1857625048.06</v>
       </c>
       <c r="J6" t="n">
-        <v>-122122222.0699999</v>
+        <v>-117121148.9100001</v>
       </c>
       <c r="K6" t="n">
-        <v>-10.17685183916666</v>
+        <v>-9.760095742500006</v>
       </c>
     </row>
     <row r="7">
@@ -689,28 +689,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>464115514.96</v>
+        <v>469321503.96</v>
       </c>
       <c r="E7" t="n">
-        <v>468775395.59</v>
+        <v>474806744.03</v>
       </c>
       <c r="F7" t="n">
-        <v>4659880.629999995</v>
+        <v>5485240.069999993</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3883233858333329</v>
+        <v>0.4571033391666661</v>
       </c>
       <c r="H7" t="n">
-        <v>1916356061.54</v>
+        <v>1974746196.97</v>
       </c>
       <c r="I7" t="n">
-        <v>1937223352.26</v>
+        <v>1996023109.36</v>
       </c>
       <c r="J7" t="n">
-        <v>20867290.72000003</v>
+        <v>21276912.38999987</v>
       </c>
       <c r="K7" t="n">
-        <v>1.738940893333336</v>
+        <v>1.773076032499989</v>
       </c>
     </row>
     <row r="8">
@@ -728,28 +728,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>464115514.96</v>
+        <v>469321503.96</v>
       </c>
       <c r="E8" t="n">
-        <v>455959739.47</v>
+        <v>460461623.41</v>
       </c>
       <c r="F8" t="n">
-        <v>-8155775.48999995</v>
+        <v>-8859880.549999952</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6796479574999958</v>
+        <v>-0.7383233791666627</v>
       </c>
       <c r="H8" t="n">
-        <v>1916356061.54</v>
+        <v>1974746196.97</v>
       </c>
       <c r="I8" t="n">
-        <v>1895858582.06</v>
+        <v>1953863714.88</v>
       </c>
       <c r="J8" t="n">
-        <v>-20497479.48000002</v>
+        <v>-20882482.08999991</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.708123290000002</v>
+        <v>-1.740206840833326</v>
       </c>
     </row>
     <row r="9">
@@ -767,28 +767,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>464115514.96</v>
+        <v>469321503.96</v>
       </c>
       <c r="E9" t="n">
-        <v>489070373.65</v>
+        <v>494146007.63</v>
       </c>
       <c r="F9" t="n">
-        <v>24954858.69</v>
+        <v>24824503.67000002</v>
       </c>
       <c r="G9" t="n">
-        <v>2.0795715575</v>
+        <v>2.068708639166668</v>
       </c>
       <c r="H9" t="n">
-        <v>1916356061.54</v>
+        <v>1974746196.97</v>
       </c>
       <c r="I9" t="n">
-        <v>1870259103.15</v>
+        <v>1931849434.13</v>
       </c>
       <c r="J9" t="n">
-        <v>-46096958.38999987</v>
+        <v>-42896762.83999991</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.841413199166656</v>
+        <v>-3.574730236666659</v>
       </c>
     </row>
   </sheetData>
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>464115514.96</v>
+        <v>469321503.96</v>
       </c>
       <c r="D2" t="n">
-        <v>464115514.96</v>
+        <v>469321503.96</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -873,16 +873,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>464115514.96</v>
+        <v>469321503.96</v>
       </c>
       <c r="D3" t="n">
-        <v>438331502.68</v>
+        <v>443546752.7</v>
       </c>
       <c r="E3" t="n">
-        <v>-25784012.27999997</v>
+        <v>-25774751.25999999</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.148667689999998</v>
+        <v>-2.147895938333332</v>
       </c>
     </row>
     <row r="4">
@@ -897,16 +897,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>464115514.96</v>
+        <v>469321503.96</v>
       </c>
       <c r="D4" t="n">
-        <v>447267377.49</v>
+        <v>453243451.72</v>
       </c>
       <c r="E4" t="n">
-        <v>-16848137.46999997</v>
+        <v>-16078052.23999995</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.404011455833331</v>
+        <v>-1.339837686666663</v>
       </c>
     </row>
     <row r="5">
@@ -921,16 +921,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>464115514.96</v>
+        <v>469321503.96</v>
       </c>
       <c r="D5" t="n">
-        <v>424713058.09</v>
+        <v>431761757.49</v>
       </c>
       <c r="E5" t="n">
-        <v>-39402456.87</v>
+        <v>-37559746.46999997</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.2835380725</v>
+        <v>-3.129978872499997</v>
       </c>
     </row>
     <row r="6">
@@ -945,16 +945,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>464115514.96</v>
+        <v>469321503.96</v>
       </c>
       <c r="D6" t="n">
-        <v>499832517.6</v>
+        <v>503296385.94</v>
       </c>
       <c r="E6" t="n">
-        <v>35717002.64000005</v>
+        <v>33974881.98000002</v>
       </c>
       <c r="F6" t="n">
-        <v>2.97641688666667</v>
+        <v>2.831240165000002</v>
       </c>
     </row>
     <row r="7">
@@ -969,16 +969,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>464115514.96</v>
+        <v>469321503.96</v>
       </c>
       <c r="D7" t="n">
-        <v>468775395.59</v>
+        <v>474806744.03</v>
       </c>
       <c r="E7" t="n">
-        <v>4659880.629999995</v>
+        <v>5485240.069999993</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3883233858333329</v>
+        <v>0.4571033391666661</v>
       </c>
     </row>
     <row r="8">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>464115514.96</v>
+        <v>469321503.96</v>
       </c>
       <c r="D8" t="n">
-        <v>455959739.47</v>
+        <v>460461623.41</v>
       </c>
       <c r="E8" t="n">
-        <v>-8155775.48999995</v>
+        <v>-8859880.549999952</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6796479574999958</v>
+        <v>-0.7383233791666627</v>
       </c>
     </row>
     <row r="9">
@@ -1017,16 +1017,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>464115514.96</v>
+        <v>469321503.96</v>
       </c>
       <c r="D9" t="n">
-        <v>489070373.65</v>
+        <v>494146007.63</v>
       </c>
       <c r="E9" t="n">
-        <v>24954858.69</v>
+        <v>24824503.67000002</v>
       </c>
       <c r="F9" t="n">
-        <v>2.0795715575</v>
+        <v>2.068708639166668</v>
       </c>
     </row>
   </sheetData>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1916356061.54</v>
+        <v>1974746196.97</v>
       </c>
       <c r="D2" t="n">
-        <v>1916356061.54</v>
+        <v>1974746196.97</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1916356061.54</v>
+        <v>1974746196.97</v>
       </c>
       <c r="D3" t="n">
-        <v>1951602159.12</v>
+        <v>2007074920.46</v>
       </c>
       <c r="E3" t="n">
-        <v>35246097.57999992</v>
+        <v>32328723.49000001</v>
       </c>
       <c r="F3" t="n">
-        <v>2.937174798333327</v>
+        <v>2.694060290833334</v>
       </c>
     </row>
     <row r="4">
@@ -1135,16 +1135,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1916356061.54</v>
+        <v>1974746196.97</v>
       </c>
       <c r="D4" t="n">
-        <v>1968379211.04</v>
+        <v>2024574398.13</v>
       </c>
       <c r="E4" t="n">
-        <v>52023149.5</v>
+        <v>49828201.16000009</v>
       </c>
       <c r="F4" t="n">
-        <v>4.335262458333333</v>
+        <v>4.152350096666674</v>
       </c>
     </row>
     <row r="5">
@@ -1159,16 +1159,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1916356061.54</v>
+        <v>1974746196.97</v>
       </c>
       <c r="D5" t="n">
-        <v>2049892910.4</v>
+        <v>2102562803.04</v>
       </c>
       <c r="E5" t="n">
-        <v>133536848.8600001</v>
+        <v>127816606.0699999</v>
       </c>
       <c r="F5" t="n">
-        <v>11.12807073833334</v>
+        <v>10.65138383916666</v>
       </c>
     </row>
     <row r="6">
@@ -1183,16 +1183,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1916356061.54</v>
+        <v>1974746196.97</v>
       </c>
       <c r="D6" t="n">
-        <v>1794233839.47</v>
+        <v>1857625048.06</v>
       </c>
       <c r="E6" t="n">
-        <v>-122122222.0699999</v>
+        <v>-117121148.9100001</v>
       </c>
       <c r="F6" t="n">
-        <v>-10.17685183916666</v>
+        <v>-9.760095742500006</v>
       </c>
     </row>
     <row r="7">
@@ -1207,16 +1207,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1916356061.54</v>
+        <v>1974746196.97</v>
       </c>
       <c r="D7" t="n">
-        <v>1937223352.26</v>
+        <v>1996023109.36</v>
       </c>
       <c r="E7" t="n">
-        <v>20867290.72000003</v>
+        <v>21276912.38999987</v>
       </c>
       <c r="F7" t="n">
-        <v>1.738940893333336</v>
+        <v>1.773076032499989</v>
       </c>
     </row>
     <row r="8">
@@ -1231,16 +1231,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1916356061.54</v>
+        <v>1974746196.97</v>
       </c>
       <c r="D8" t="n">
-        <v>1895858582.06</v>
+        <v>1953863714.88</v>
       </c>
       <c r="E8" t="n">
-        <v>-20497479.48000002</v>
+        <v>-20882482.08999991</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.708123290000002</v>
+        <v>-1.740206840833326</v>
       </c>
     </row>
     <row r="9">
@@ -1255,16 +1255,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1916356061.54</v>
+        <v>1974746196.97</v>
       </c>
       <c r="D9" t="n">
-        <v>1870259103.15</v>
+        <v>1931849434.13</v>
       </c>
       <c r="E9" t="n">
-        <v>-46096958.38999987</v>
+        <v>-42896762.83999991</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.841413199166656</v>
+        <v>-3.574730236666659</v>
       </c>
     </row>
   </sheetData>
